--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486553_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486553_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7187</v>
+        <v>3.3507</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4758</v>
+        <v>4.9228</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7571</v>
+        <v>-1.5722</v>
       </c>
       <c r="G2" t="n">
         <v>5.5846</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9953</v>
+        <v>-1.3633</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4675</v>
+        <v>-0.0204</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5278</v>
+        <v>-1.3429</v>
       </c>
       <c r="V2" t="n">
         <v>1.3045</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.114</v>
+        <v>1.9993</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6135</v>
+        <v>2.581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5004999999999999</v>
+        <v>-0.5817</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5904</v>
+        <v>-1.0492</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1568</v>
+        <v>0.3923</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4335</v>
+        <v>-1.4415</v>
       </c>
       <c r="J3" t="n">
-        <v>4.102</v>
+        <v>1.2005</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0111</v>
+        <v>1.3901</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0909</v>
+        <v>-0.1896</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4883</v>
+        <v>-2.2497</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1457</v>
+        <v>-0.9978</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3426</v>
+        <v>-1.2519</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8461</v>
+        <v>-0.8862</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2091</v>
+        <v>-0.3569</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0552</v>
+        <v>-0.5294</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7602</v>
+        <v>2.6297</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.8249</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8102</v>
+        <v>1.9258</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8591</v>
+        <v>1.6355</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0488</v>
+        <v>0.2902</v>
       </c>
       <c r="G4" t="n">
         <v>1.1676</v>
@@ -766,13 +766,13 @@
         <v>3.2626</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.49</v>
+        <v>-1.3744</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1526</v>
+        <v>-0.0709</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.6426</v>
+        <v>-1.3036</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2671</v>
+        <v>1.6362</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9104</v>
+        <v>1.1665</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6434</v>
+        <v>0.4697</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0492</v>
+        <v>4.5904</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3923</v>
+        <v>3.1568</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4415</v>
+        <v>1.4335</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2005</v>
+        <v>4.102</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3901</v>
+        <v>3.0111</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1896</v>
+        <v>1.0909</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2497</v>
+        <v>0.4883</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9978</v>
+        <v>0.1457</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2519</v>
+        <v>0.3426</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
         <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6184</v>
+        <v>-1.324</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0274</v>
+        <v>-0.2379</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.591</v>
+        <v>-1.086</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6297</v>
+        <v>-0.7602</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8249</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.4741</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.26</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9228</v>
+        <v>0.3988</v>
       </c>
       <c r="G6" t="n">
         <v>0.9593</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.949</v>
+        <v>-1.1377</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.276</v>
+        <v>-0.8</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5578</v>
+        <v>0.1061</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6544</v>
+        <v>1.1765</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2122</v>
+        <v>-1.0704</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7403</v>
+        <v>-2.0362</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.514</v>
+        <v>-0.3469</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2543</v>
+        <v>-1.6893</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6959</v>
+        <v>-0.036</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0452</v>
+        <v>0.4015</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7412</v>
+        <v>-0.4374</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9556</v>
+        <v>-2.0003</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4688</v>
+        <v>-0.7484</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4869</v>
+        <v>-1.2519</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9505</v>
+        <v>-1.0524</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0036</v>
+        <v>-0.0024</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9542</v>
+        <v>-1.05</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>3.1947</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>3.3899</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6569</v>
+        <v>-0.7813</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5059</v>
+        <v>0.4309</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1629</v>
+        <v>-1.2122</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0362</v>
+        <v>0.7403</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3469</v>
+        <v>-0.514</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6893</v>
+        <v>1.2543</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.036</v>
+        <v>1.6959</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4015</v>
+        <v>-0.0452</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4374</v>
+        <v>1.7412</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0003</v>
+        <v>-0.9556</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7484</v>
+        <v>-0.4688</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2519</v>
+        <v>-0.4869</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8154</v>
+        <v>-1.1741</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.2199</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1425</v>
+        <v>-0.9542</v>
       </c>
       <c r="V8" t="n">
-        <v>3.1947</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5449</v>
+        <v>-4.9037</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8259</v>
+        <v>-3.5595</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.719</v>
+        <v>-1.3442</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6138</v>
+        <v>-3.265</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2829</v>
+        <v>-2.2323</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3309</v>
+        <v>-1.0327</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6981</v>
+        <v>-1.8983</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1674</v>
+        <v>-1.2679</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8655</v>
+        <v>-0.6303</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9158</v>
+        <v>-1.3668</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4504</v>
+        <v>-0.9643</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4654</v>
+        <v>-0.4024</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8085</v>
+        <v>-0.2488</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6992</v>
+        <v>0.1658</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8907</v>
+        <v>-0.4146</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7395</v>
+        <v>-2.2599</v>
       </c>
       <c r="W10" t="n">
         <v>-0.7395</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7919</v>
+        <v>-5.7241</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4477</v>
+        <v>-3.9435</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3442</v>
+        <v>-1.7806</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.265</v>
+        <v>-4.6138</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2323</v>
+        <v>-0.2829</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0327</v>
+        <v>-4.3309</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8983</v>
+        <v>-2.6981</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2679</v>
+        <v>0.1674</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6303</v>
+        <v>-2.8655</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3668</v>
+        <v>-1.9158</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9643</v>
+        <v>-0.4504</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4024</v>
+        <v>-1.4654</v>
       </c>
       <c r="P11" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.137</v>
+        <v>-0.3707</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2776</v>
+        <v>0.5816</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4146</v>
+        <v>-0.9523</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="W11" t="n">
         <v>-0.7395</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2326</v>
+        <v>-7.2942</v>
       </c>
       <c r="E12" t="n">
         <v>-4.6442</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5884</v>
+        <v>-2.65</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9169</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7501</v>
+        <v>-0.8117</v>
       </c>
       <c r="T12" t="n">
         <v>0.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8222</v>
+        <v>-0.8839</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3904</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.6638</v>
+        <v>-10.6636</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.246200000000002</v>
+        <v>-1.2462</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.4177</v>
+        <v>-9.4176</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7569</v>
+        <v>-1.756900000000001</v>
       </c>
       <c r="H13" t="n">
         <v>5.792999999999999</v>
@@ -1447,7 +1447,7 @@
         <v>10.9662</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7686999999999991</v>
+        <v>-0.7687</v>
       </c>
       <c r="M13" t="n">
         <v>-11.9547</v>
@@ -1471,10 +1471,10 @@
         <v>-10.1903</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4265</v>
+        <v>-0.4266</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.763800000000002</v>
+        <v>-9.763900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.2839</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3033</v>
+        <v>4.7568</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2687</v>
+        <v>2.604</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0346</v>
+        <v>2.1528</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7326</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6884</v>
+        <v>1.1419</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9181</v>
+        <v>1.2534</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2297</v>
+        <v>-0.1115</v>
       </c>
       <c r="V14" t="n">
         <v>3.3899</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0122</v>
+        <v>3.6683</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9796</v>
+        <v>1.4177</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0325</v>
+        <v>2.2506</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0062</v>
+        <v>2.5729</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5081</v>
+        <v>-0.958</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4981</v>
+        <v>3.5309</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4795</v>
+        <v>3.0766</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7911</v>
+        <v>-0.1762</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6885</v>
+        <v>3.2528</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5266999999999999</v>
+        <v>-0.5038</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2829</v>
+        <v>-0.7819</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8096</v>
+        <v>0.2781</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>3.0451</v>
       </c>
       <c r="S15" t="n">
-        <v>2.158</v>
+        <v>0.9647</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1102</v>
+        <v>0.5384</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0478</v>
+        <v>0.4263</v>
       </c>
       <c r="V15" t="n">
+        <v>-0.5218</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.717</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9039</v>
+        <v>3.1311</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8589</v>
+        <v>2.9597</v>
       </c>
       <c r="F16" t="n">
-        <v>2.045</v>
+        <v>0.1714</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5729</v>
+        <v>1.4885</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.958</v>
+        <v>1.2591</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5309</v>
+        <v>0.2295</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0766</v>
+        <v>3.0267</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1762</v>
+        <v>2.7374</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2528</v>
+        <v>0.2893</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5038</v>
+        <v>-1.5381</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7819</v>
+        <v>-1.4783</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2781</v>
+        <v>-0.0598</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0451</v>
+        <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2003</v>
+        <v>1.0121</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0204</v>
+        <v>0.8051</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2207</v>
+        <v>0.207</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5218</v>
+        <v>0.4129</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>1.5204</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.717</v>
+        <v>-1.1075</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4586</v>
+        <v>2.8427</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2652</v>
+        <v>0.377</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1934</v>
+        <v>2.4657</v>
       </c>
       <c r="G17" t="n">
         <v>2.507</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5259</v>
+        <v>-0.1418</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0925</v>
+        <v>0.2043</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.3461</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4019</v>
+        <v>1.9819</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3929</v>
+        <v>0.8621</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9911</v>
+        <v>1.1199</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4411</v>
+        <v>2.0062</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.469</v>
+        <v>0.5081</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0279</v>
+        <v>1.4981</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2213</v>
+        <v>1.4795</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1246</v>
+        <v>0.7911</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3459</v>
+        <v>0.6885</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6624</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3444</v>
+        <v>-0.2829</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.318</v>
+        <v>0.8096</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2557</v>
+        <v>1.1278</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0417</v>
+        <v>0.9926</v>
       </c>
       <c r="U18" t="n">
-        <v>0.214</v>
+        <v>0.1352</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9347</v>
+        <v>-0.717</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0674</v>
+        <v>1.6504</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6186</v>
+        <v>2.6106</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4488</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4885</v>
+        <v>-1.4411</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2591</v>
+        <v>-1.469</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2295</v>
+        <v>0.0279</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0267</v>
+        <v>0.2213</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7374</v>
+        <v>-0.1246</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2893</v>
+        <v>0.3459</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5381</v>
+        <v>-1.6624</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4783</v>
+        <v>-1.3444</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0598</v>
+        <v>-0.318</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6101</v>
+        <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0516</v>
+        <v>1.5042</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.536</v>
+        <v>1.2594</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4844</v>
+        <v>0.2448</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4129</v>
+        <v>0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1075</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4219</v>
+        <v>1.2665</v>
       </c>
       <c r="E20" t="n">
-        <v>2.706</v>
+        <v>2.3708</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2841</v>
+        <v>-1.1043</v>
       </c>
       <c r="G20" t="n">
         <v>0.14</v>
@@ -2014,13 +2014,13 @@
         <v>2.6101</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9337</v>
+        <v>1.7782</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6307</v>
+        <v>1.2954</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3029</v>
+        <v>0.4828</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0868</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2202</v>
+        <v>0.7037</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2928</v>
+        <v>0.6222</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0726</v>
+        <v>0.0815</v>
       </c>
       <c r="G21" t="n">
         <v>0.0438</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3068</v>
+        <v>0.7904</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3531</v>
+        <v>0.6826</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V21" t="n">
         <v>0.7395</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6894</v>
+        <v>-0.4757</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2427</v>
+        <v>-0.7631</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4467</v>
+        <v>0.2875</v>
       </c>
       <c r="G22" t="n">
         <v>0.4696</v>
@@ -2170,13 +2170,13 @@
         <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6341</v>
+        <v>1.4691</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2147</v>
+        <v>1.2089</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4194</v>
+        <v>0.2602</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1093</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7626</v>
+        <v>-0.7402</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7454</v>
+        <v>-0.2983</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0173</v>
+        <v>-0.4418</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2549</v>
@@ -2248,13 +2248,13 @@
         <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4435</v>
+        <v>0.5789</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1166</v>
+        <v>0.5636</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5601</v>
+        <v>0.0153</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8042</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.0524</v>
+        <v>-6.6317</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4625</v>
+        <v>-3.3449</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5899</v>
+        <v>-3.2868</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0423</v>
@@ -2326,13 +2326,13 @@
         <v>2.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0342</v>
+        <v>1.455</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1574</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1917</v>
+        <v>0.4948</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6518</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.6638</v>
+        <v>12.1538</v>
       </c>
       <c r="E25" t="n">
-        <v>9.4175</v>
+        <v>9.417800000000003</v>
       </c>
       <c r="F25" t="n">
-        <v>1.246</v>
+        <v>2.7363</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7571</v>
+        <v>1.757099999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-5.7931</v>
@@ -2404,13 +2404,13 @@
         <v>20.6633</v>
       </c>
       <c r="S25" t="n">
-        <v>10.1902</v>
+        <v>11.6805</v>
       </c>
       <c r="T25" t="n">
-        <v>9.763799999999998</v>
+        <v>9.7639</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4264000000000001</v>
+        <v>1.9166</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2839</v>
